--- a/reports/jobs_2026-09-13.xlsx
+++ b/reports/jobs_2026-09-13.xlsx
@@ -3932,15 +3932,35 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>Darwinbox</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>https://darwinbox.com/careers</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
+Call log:
+  - navigating to "https://darwinbox.com/careers", waiting until "networkidle"
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>Nykaa</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>https://www.nykaa.com/careers</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: net::ERR_HTTP2_PROTOCOL_ERROR at https://www.nykaa.com/careers
 Call log:
@@ -3949,18 +3969,18 @@
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
+    <row r="10">
+      <c r="A10" t="inlineStr">
         <is>
           <t>Juspay</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>https://juspay.io/careers</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
@@ -3969,18 +3989,18 @@
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
+    <row r="11">
+      <c r="A11" t="inlineStr">
         <is>
           <t>MakeMyTrip</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>https://careers.makemytrip.com/</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
@@ -3989,26 +4009,6 @@
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>FirstCry</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>https://www.firstcry.com/careers</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
-Call log:
-  - navigating to "https://www.firstcry.com/careers", waiting until "networkidle"
-</t>
-        </is>
-      </c>
-    </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
